--- a/Required Functions.xlsx
+++ b/Required Functions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Class</t>
   </si>
@@ -34,12 +34,6 @@
     <t>Donor</t>
   </si>
   <si>
-    <t>updateHealthMetrics()</t>
-  </si>
-  <si>
-    <t>A method/service to manage health data related to a donor's eligibility.</t>
-  </si>
-  <si>
     <t>checkEligibility()</t>
   </si>
   <si>
@@ -146,6 +140,12 @@
   </si>
   <si>
     <t>A service to dispatch notifications (SMS, email) based on status changes (e.g., request acceptance).</t>
+  </si>
+  <si>
+    <t>implemented</t>
+  </si>
+  <si>
+    <t>future implementation</t>
   </si>
 </sst>
 </file>
@@ -445,7 +445,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -457,29 +457,29 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
@@ -500,8 +500,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
+      <c r="A8" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -511,8 +511,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
+      <c r="A9" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>21</v>
@@ -522,8 +522,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
+      <c r="A10" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -533,8 +533,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
+      <c r="A11" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>25</v>
@@ -544,11 +544,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
+      <c r="A12" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -556,40 +556,40 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>29</v>
+      <c r="A14" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -599,35 +599,34 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
+      <c r="A17" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
+      <c r="A18" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="1" t="s">
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
     </row>
